--- a/data/raw/infrastructure/SSP2/infra_lifetime_weibull.xlsx
+++ b/data/raw/infrastructure/SSP2/infra_lifetime_weibull.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Academic\Chapter2\2. dMFA\ELMA\grid_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67871F9F-5B75-4D78-B9BC-F3CB8572DF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B53A06C-6901-42EB-962B-6D6DB8B78509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{464C6650-2143-4BE9-97C5-418239FBCB67}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="operational_lifetime" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">operational_lifetime!$A$1:$B$15</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">operational_lifetime!$A$1:$B$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>scale</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>Bridge Class 7</t>
+  </si>
+  <si>
+    <t>Bridge Class 8</t>
+  </si>
+  <si>
+    <t>Bridge Class 9</t>
+  </si>
+  <si>
+    <t>Road Class 9</t>
+  </si>
+  <si>
+    <t>Road Class 10</t>
   </si>
 </sst>
 </file>
@@ -142,9 +154,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -179,12 +190,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3E1841BC-2732-493B-ABB8-B5F9FBE06315}" name="operational_lifetime" displayName="operational_lifetime" ref="A1:C15" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C15" xr:uid="{3E1841BC-2732-493B-ABB8-B5F9FBE06315}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3E1841BC-2732-493B-ABB8-B5F9FBE06315}" name="operational_lifetime" displayName="operational_lifetime" ref="A1:C17" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C17" xr:uid="{3E1841BC-2732-493B-ABB8-B5F9FBE06315}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6D4C5F8B-FC84-424B-8C77-07A158A197B4}" uniqueName="1" name="Traffic" queryTableFieldId="1" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{4EF24F0B-1F58-441A-9BCD-EBD15CDD80BE}" uniqueName="2" name="scale" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{AEA05B28-29E7-417B-8C11-62F8A35589BF}" uniqueName="3" name="shape" queryTableFieldId="3"/>
+    <tableColumn id="2" xr3:uid="{4EF24F0B-1F58-441A-9BCD-EBD15CDD80BE}" uniqueName="2" name="shape" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{AEA05B28-29E7-417B-8C11-62F8A35589BF}" uniqueName="3" name="scale" queryTableFieldId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -507,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC527D26-8B05-46BB-B5A4-38081B129E92}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" customWidth="1"/>
@@ -519,10 +530,10 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -603,91 +614,135 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>300</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>1.976</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>134.30000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>105.62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>1.855</v>
+        <v>1.976</v>
       </c>
       <c r="C12">
-        <v>95.15</v>
+        <v>134.30000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>1.923</v>
+        <v>1.77</v>
       </c>
       <c r="C13">
-        <v>92</v>
+        <v>105.62</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>1.887</v>
+        <v>1.855</v>
       </c>
       <c r="C14">
-        <v>81.349999999999994</v>
+        <v>95.15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>2.016</v>
+        <v>1.923</v>
       </c>
       <c r="C15">
-        <v>67.83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>1.887</v>
+      </c>
+      <c r="C16">
+        <v>81.349999999999994</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>2.016</v>
+      </c>
+      <c r="C17">
+        <v>67.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16">
-        <v>1000</v>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
